--- a/formatos_hoja_de_calculo/PLANTILLA_PARVULARIA_PRIMER_GRADO_NUEVA.xlsx
+++ b/formatos_hoja_de_calculo/PLANTILLA_PARVULARIA_PRIMER_GRADO_NUEVA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\registro_academico\formatos_hoja_de_calculo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB918EB-48BC-49CB-B08D-D5183E194F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3893C2D4-E841-4B3B-AE70-FFFAEB697208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28125" windowHeight="14850" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -241,9 +241,6 @@
     <t>DP1-PG-05-A</t>
   </si>
   <si>
-    <t>Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.</t>
-  </si>
-  <si>
     <t>DP1-PG-05-B</t>
   </si>
   <si>
@@ -1088,6 +1085,9 @@
   </si>
   <si>
     <t>Cuidar de sí mismo identificando aquellas acciones, alimentos y hábitos que le generan bienestar, al mismo tiempo que incorpora algunas prácticas de reutilización de materiales y separación de desechos sólidos siempre que le sea posible, contribuyendo al cuidado colectivo de su comunidad.</t>
+  </si>
+  <si>
+    <t>Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.</t>
   </si>
 </sst>
 </file>
@@ -1483,121 +1483,121 @@
     <row r="1" spans="1:40" ht="149.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="AN1" s="3" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:40" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2849,33 +2849,33 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="51" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>70</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>39</v>
@@ -2883,31 +2883,31 @@
     </row>
     <row r="22" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>39</v>
@@ -2915,31 +2915,31 @@
     </row>
     <row r="26" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>39</v>
@@ -2947,31 +2947,31 @@
     </row>
     <row r="30" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>39</v>
@@ -2979,31 +2979,31 @@
     </row>
     <row r="34" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>39</v>
@@ -3011,31 +3011,31 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>39</v>
@@ -3043,31 +3043,31 @@
     </row>
     <row r="42" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>39</v>
@@ -3075,31 +3075,31 @@
     </row>
     <row r="46" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>39</v>
@@ -3107,31 +3107,31 @@
     </row>
     <row r="50" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>129</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>39</v>
@@ -3139,31 +3139,31 @@
     </row>
     <row r="54" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>39</v>
@@ -3171,31 +3171,31 @@
     </row>
     <row r="58" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>39</v>
@@ -3203,31 +3203,31 @@
     </row>
     <row r="62" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>147</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>150</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>39</v>
@@ -3235,31 +3235,31 @@
     </row>
     <row r="66" spans="1:2" ht="51" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>153</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>157</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>39</v>
@@ -3267,31 +3267,31 @@
     </row>
     <row r="70" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>160</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>162</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>39</v>
@@ -3299,31 +3299,31 @@
     </row>
     <row r="74" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>169</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>171</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>39</v>
@@ -3331,31 +3331,31 @@
     </row>
     <row r="78" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>174</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>39</v>
@@ -3363,31 +3363,31 @@
     </row>
     <row r="82" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>39</v>
@@ -3395,31 +3395,31 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>188</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>192</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>39</v>
@@ -3427,31 +3427,31 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>195</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>197</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>199</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>39</v>
@@ -3459,31 +3459,31 @@
     </row>
     <row r="94" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>202</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>204</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>206</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>39</v>
@@ -3491,31 +3491,31 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>209</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>211</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>213</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>39</v>
@@ -3523,31 +3523,31 @@
     </row>
     <row r="102" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>216</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>218</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>220</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>39</v>
@@ -3555,31 +3555,31 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>223</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>225</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>227</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>39</v>
@@ -3587,31 +3587,31 @@
     </row>
     <row r="110" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>230</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>232</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>234</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>39</v>
@@ -3619,31 +3619,31 @@
     </row>
     <row r="114" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>237</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>239</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>241</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>39</v>
@@ -3651,31 +3651,31 @@
     </row>
     <row r="118" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>244</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
+        <v>246</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>248</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>39</v>
@@ -3683,31 +3683,31 @@
     </row>
     <row r="122" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>251</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
+        <v>253</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>255</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>39</v>
@@ -3715,31 +3715,31 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>258</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
+        <v>260</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
+        <v>262</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>39</v>
@@ -3747,31 +3747,31 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>265</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>267</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>269</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>39</v>
@@ -3779,31 +3779,31 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>272</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>274</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>276</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>39</v>
@@ -3811,31 +3811,31 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>279</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
+        <v>281</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
+        <v>283</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>39</v>
@@ -3843,31 +3843,31 @@
     </row>
     <row r="142" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
+        <v>286</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>288</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>290</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>39</v>
@@ -3875,31 +3875,31 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
+        <v>293</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
+        <v>295</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>297</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>39</v>
@@ -3907,31 +3907,31 @@
     </row>
     <row r="150" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
+        <v>300</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
+        <v>302</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
+        <v>304</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>39</v>
@@ -3939,31 +3939,31 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
+        <v>307</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>309</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
+        <v>311</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>39</v>
